--- a/5/search/FY5_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY5_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,34 +492,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="B2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>12256.68074623982</v>
+        <v>12237.29596043756</v>
       </c>
       <c r="F2" t="n">
-        <v>-489.3758088163006</v>
+        <v>-503.109039363542</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>12207.93850009161</v>
+        <v>12180.09315747038</v>
       </c>
       <c r="I2" t="n">
-        <v>-390.3184848042546</v>
+        <v>-390.8422173158076</v>
       </c>
       <c r="J2" t="n">
-        <v>1296.864</v>
+        <v>1296.031</v>
       </c>
       <c r="K2" t="n">
         <v>3.800000000000001</v>
@@ -530,75 +530,75 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116.2</v>
+        <v>118</v>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>135.4</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>12207.93850009161</v>
+        <v>12237.20260478549</v>
       </c>
       <c r="F3" t="n">
-        <v>-390.3184848042547</v>
+        <v>-565.3867511228157</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>12207.93850009161</v>
+        <v>12141.85293038367</v>
       </c>
       <c r="I3" t="n">
-        <v>-390.3184848042547</v>
+        <v>-386.0600950131676</v>
       </c>
       <c r="J3" t="n">
-        <v>1300</v>
+        <v>1288.975</v>
       </c>
       <c r="K3" t="n">
-        <v>3.700000000000001</v>
+        <v>3.799999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116.2</v>
+        <v>120.2</v>
       </c>
       <c r="B4" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
-        <v>12232.30962316571</v>
+        <v>12185.10768645902</v>
       </c>
       <c r="F4" t="n">
-        <v>-439.8471468102778</v>
+        <v>-599.8748208349984</v>
       </c>
       <c r="G4" t="n">
         <v>1300</v>
       </c>
       <c r="H4" t="n">
-        <v>12207.93850009161</v>
+        <v>12062.87383942787</v>
       </c>
       <c r="I4" t="n">
-        <v>-390.3184848042548</v>
+        <v>-389.8560439602481</v>
       </c>
       <c r="J4" t="n">
-        <v>1299.216</v>
+        <v>1284.124</v>
       </c>
       <c r="K4" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -606,75 +606,75 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116.2</v>
+        <v>126</v>
       </c>
       <c r="B5" t="n">
-        <v>137.5</v>
+        <v>133.4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>12235.0911100383</v>
+        <v>12059.07336813021</v>
       </c>
       <c r="F5" t="n">
-        <v>-445.4998745392259</v>
+        <v>-704.9255954045841</v>
       </c>
       <c r="G5" t="n">
         <v>1300</v>
       </c>
       <c r="H5" t="n">
-        <v>12210.80828813476</v>
+        <v>11823.84171016276</v>
       </c>
       <c r="I5" t="n">
-        <v>-396.1506642071378</v>
+        <v>-381.1569942557301</v>
       </c>
       <c r="J5" t="n">
-        <v>1299.216</v>
+        <v>1255.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116.2</v>
+        <v>115.4</v>
       </c>
       <c r="B6" t="n">
-        <v>137.5</v>
+        <v>138.5</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>12210.80828813476</v>
+        <v>12251.46529869817</v>
       </c>
       <c r="F6" t="n">
-        <v>-396.1506642071377</v>
+        <v>-423.5895804242539</v>
       </c>
       <c r="G6" t="n">
         <v>1300</v>
       </c>
       <c r="H6" t="n">
-        <v>12210.80828813476</v>
+        <v>12233.64304390527</v>
       </c>
       <c r="I6" t="n">
-        <v>-396.1506642071377</v>
+        <v>-386.0559990057836</v>
       </c>
       <c r="J6" t="n">
-        <v>1300</v>
+        <v>1299.559</v>
       </c>
       <c r="K6" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -682,113 +682,113 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117.8</v>
+        <v>118</v>
       </c>
       <c r="B7" t="n">
-        <v>139.5</v>
+        <v>129.4</v>
       </c>
       <c r="C7" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
-        <v>12206.25657680554</v>
+        <v>12234.55478517137</v>
       </c>
       <c r="F7" t="n">
-        <v>-494.5316382814487</v>
+        <v>-560.4069266990912</v>
       </c>
       <c r="G7" t="n">
         <v>1300</v>
       </c>
       <c r="H7" t="n">
-        <v>12154.20782774361</v>
+        <v>12143.43035483463</v>
       </c>
       <c r="I7" t="n">
-        <v>-395.8124014474453</v>
+        <v>-389.0267989251735</v>
       </c>
       <c r="J7" t="n">
-        <v>1296.864</v>
+        <v>1288.975</v>
       </c>
       <c r="K7" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="D8" t="n">
         <v>1.2</v>
       </c>
       <c r="E8" t="n">
-        <v>12229.5292701585</v>
+        <v>12245.74018373272</v>
       </c>
       <c r="F8" t="n">
-        <v>-538.6722289446814</v>
+        <v>-519.6817607134456</v>
       </c>
       <c r="G8" t="n">
         <v>1300</v>
       </c>
       <c r="H8" t="n">
-        <v>12151.1763145814</v>
+        <v>12181.99991756929</v>
       </c>
       <c r="I8" t="n">
-        <v>-390.0626251085474</v>
+        <v>-394.5844447173988</v>
       </c>
       <c r="J8" t="n">
         <v>1292.944</v>
       </c>
       <c r="K8" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119.4</v>
+        <v>115.4</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C9" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>12200.6123276131</v>
+        <v>12235.63759227559</v>
       </c>
       <c r="F9" t="n">
-        <v>-581.3154299718833</v>
+        <v>-390.2565081175978</v>
       </c>
       <c r="G9" t="n">
         <v>1300</v>
       </c>
       <c r="H9" t="n">
-        <v>12092.22077881488</v>
+        <v>12235.63759227559</v>
       </c>
       <c r="I9" t="n">
-        <v>-388.9514204765455</v>
+        <v>-390.2565081175978</v>
       </c>
       <c r="J9" t="n">
-        <v>1287.456</v>
+        <v>1300</v>
       </c>
       <c r="K9" t="n">
-        <v>3.699999999999999</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B10" t="n">
-        <v>139.5</v>
+        <v>136.5</v>
       </c>
       <c r="C10" t="n">
         <v>12.6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>12180.23220227457</v>
+        <v>12219.18173949795</v>
       </c>
       <c r="F10" t="n">
-        <v>-445.1720198644471</v>
+        <v>-467.5578790484262</v>
       </c>
       <c r="G10" t="n">
         <v>1300</v>
       </c>
       <c r="H10" t="n">
-        <v>12154.20782774361</v>
+        <v>12181.99991756928</v>
       </c>
       <c r="I10" t="n">
-        <v>-395.8124014474453</v>
+        <v>-394.5844447173989</v>
       </c>
       <c r="J10" t="n">
-        <v>1299.216</v>
+        <v>1298.236</v>
       </c>
       <c r="K10" t="n">
-        <v>3.600000000000001</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -834,37 +834,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116.2</v>
+        <v>118.6</v>
       </c>
       <c r="B11" t="n">
-        <v>138.5</v>
+        <v>136</v>
       </c>
       <c r="C11" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
-        <v>12253.98756053779</v>
+        <v>12218.77488784093</v>
       </c>
       <c r="F11" t="n">
-        <v>-483.9025327612874</v>
+        <v>-567.1317841015357</v>
       </c>
       <c r="G11" t="n">
         <v>1300</v>
       </c>
       <c r="H11" t="n">
-        <v>12205.06871204846</v>
+        <v>12121.12174882105</v>
       </c>
       <c r="I11" t="n">
-        <v>-384.4863054013717</v>
+        <v>-388.0232571142276</v>
       </c>
       <c r="J11" t="n">
-        <v>1296.864</v>
+        <v>1288.975</v>
       </c>
       <c r="K11" t="n">
-        <v>3.600000000000001</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
